--- a/Timesheet_Dispatcher/Data/Config.xlsx
+++ b/Timesheet_Dispatcher/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sudha.peramuthu\Documents\Sudha\uipath-timesheet-processing\Timesheet_Dispatcher\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9CD17D-7CA3-4504-9C53-F7A23ECCC07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0802C68-8E8E-49A2-965B-3C32B4649E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
